--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>chicago_american_1835; chicago_democrat_1833_1835</t>
+          <t>chicago_american_1835; chicago_democrat_1833_1835; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>chicago_democrat_1833_1835</t>
+          <t>chicago_democrat_1833_1835; fergus_1843_old_settler_death_notices</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>chicago_democrat_1833_1835</t>
+          <t>chicago_democrat_1833_1835; fergus_1843_old_settler_death_notices</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -878,7 +878,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; census_1840_chicago_familysearch_images; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -878,7 +878,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -878,7 +878,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; fergus_chicago_directory_1843; isa_public_domain_land_tract_sales; norris_directory_1844</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; census_1840_chicago_familysearch_images; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -878,7 +878,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; chicago_democrat_1833_11_26; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1839; isa_public_domain_land_tract_sales</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; chicago_voter_lists_1833_1835_irad</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; census_1840_chicago_familysearch_images; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>chicago_american_1835; chicago_democrat_1833_1835; isa_public_domain_land_tract_sales</t>
+          <t>chicago_american_1835; chicago_democrat_1833_1835</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>

--- a/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
+++ b/chicago/reference/resident-research/T-0442/T-0442_resident_research_working.xlsx
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>andreas_1884_v1; calumet_club_early_chicago_1879; census_1840_chicago_familysearch_images; chicago_american_1835; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; norris_directory_1844</t>
+          <t>andreas_1884_v1; calumet_club_early_chicago_1879; census_1840_chicago_familysearch_images; chicago_american_1835; chicago_antiquities_american_fur_co; chicago_democrat_1833_1835; chicago_voter_lists_1833_1835_irad; fergus_chicago_directory_1843; norris_directory_1844</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
